--- a/Fundamental_Booster.xlsx
+++ b/Fundamental_Booster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All_Project_Data\EXCEL_PROJECTS\Project 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C21DA6-C94B-4245-BC6B-1D85B3B70956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBD4BBB-A281-4E28-A9E1-536F0AD5F90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{9A681CB3-562D-4114-9D0B-20B213D7B8DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9A681CB3-562D-4114-9D0B-20B213D7B8DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Students Grade " sheetId="1" r:id="rId1"/>
@@ -1035,90 +1035,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1136,6 +1052,90 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1491,44 +1491,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="78"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2311,16 +2311,16 @@
       <c r="L30" s="25"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="77"/>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="78"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="88"/>
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
@@ -2330,15 +2330,15 @@
       <c r="A32" s="11">
         <v>3</v>
       </c>
-      <c r="B32" s="81" t="s">
+      <c r="B32" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
@@ -2348,15 +2348,15 @@
       <c r="A33" s="11">
         <v>4</v>
       </c>
-      <c r="B33" s="81" t="s">
+      <c r="B33" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
       <c r="I33" s="25"/>
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
@@ -2372,16 +2372,16 @@
       <c r="L34" s="25"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="107" t="s">
+      <c r="A35" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="107" t="s">
+      <c r="C35" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="108" t="s">
+      <c r="D35" s="80" t="s">
         <v>159</v>
       </c>
       <c r="E35" s="55"/>
@@ -2402,7 +2402,7 @@
         <f ca="1">DATEDIF(B36,TODAY(),"Y")</f>
         <v>23</v>
       </c>
-      <c r="D36" s="106" t="str">
+      <c r="D36" s="78" t="str">
         <f>LEFT(A36,FIND(" ",A36,1))</f>
         <v xml:space="preserve">Ananya </v>
       </c>
@@ -2424,7 +2424,7 @@
         <f ca="1">DATEDIF(B37,TODAY(),"Y")</f>
         <v>21</v>
       </c>
-      <c r="D37" s="106" t="str">
+      <c r="D37" s="78" t="str">
         <f t="shared" ref="D37:D40" si="4">LEFT(A37,FIND(" ",A37,1))</f>
         <v xml:space="preserve">Rohan </v>
       </c>
@@ -2446,7 +2446,7 @@
         <f ca="1">DATEDIF(B38,TODAY(),"Y")</f>
         <v>20</v>
       </c>
-      <c r="D38" s="106" t="str">
+      <c r="D38" s="78" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">Priya </v>
       </c>
@@ -2468,7 +2468,7 @@
         <f ca="1">DATEDIF(B39,TODAY(),"Y")</f>
         <v>17</v>
       </c>
-      <c r="D39" s="106" t="str">
+      <c r="D39" s="78" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">Neha </v>
       </c>
@@ -2490,7 +2490,7 @@
         <f ca="1">DATEDIF(B40,TODAY(),"Y")</f>
         <v>23</v>
       </c>
-      <c r="D40" s="106" t="str">
+      <c r="D40" s="78" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">Yash </v>
       </c>
@@ -2530,16 +2530,16 @@
       <c r="L42" s="25"/>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="78"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="87"/>
+      <c r="E43" s="87"/>
+      <c r="F43" s="87"/>
+      <c r="G43" s="87"/>
+      <c r="H43" s="88"/>
       <c r="I43" s="25"/>
       <c r="J43" s="25"/>
       <c r="K43" s="25"/>
@@ -2549,15 +2549,15 @@
       <c r="A44" s="11">
         <v>5</v>
       </c>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="84"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="90"/>
+      <c r="F44" s="90"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="91"/>
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
       <c r="K44" s="25"/>
@@ -2567,20 +2567,20 @@
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="85"/>
+      <c r="B46" s="92"/>
+      <c r="C46" s="92"/>
       <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="86">
+      <c r="A47" s="93">
         <f>COUNTIFS(C9:C28,"&gt;"&amp;50)</f>
         <v>19</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="B47" s="93"/>
+      <c r="C47" s="93"/>
       <c r="D47" s="27"/>
       <c r="E47" s="27"/>
       <c r="F47" s="27"/>
@@ -2606,30 +2606,30 @@
       <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="76" t="s">
+      <c r="A50" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="77"/>
-      <c r="C50" s="77"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="78"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="88"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>6</v>
       </c>
-      <c r="B51" s="87" t="s">
+      <c r="B51" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="88"/>
-      <c r="D51" s="88"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="88"/>
-      <c r="H51" s="89"/>
+      <c r="C51" s="95"/>
+      <c r="D51" s="95"/>
+      <c r="E51" s="95"/>
+      <c r="F51" s="95"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="96"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="29"/>
@@ -2639,21 +2639,21 @@
       <c r="H52" s="28"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="93" t="s">
+      <c r="A53" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="93"/>
-      <c r="C53" s="93"/>
-      <c r="D53" s="93"/>
+      <c r="B53" s="99"/>
+      <c r="C53" s="99"/>
+      <c r="D53" s="99"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="94">
+      <c r="A54" s="100">
         <f>AVERAGEIFS($H$9:$H$28,H9:$H$28,"&gt;60")</f>
         <v>73.625000000000014</v>
       </c>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="60"/>
@@ -2668,51 +2668,51 @@
       <c r="D56" s="60"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="76" t="s">
+      <c r="A57" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="77"/>
-      <c r="E57" s="77"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="78"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="87"/>
+      <c r="G57" s="87"/>
+      <c r="H57" s="88"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>7</v>
       </c>
-      <c r="B58" s="81" t="s">
+      <c r="B58" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="85"/>
+      <c r="E58" s="85"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="85"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="90" t="s">
+      <c r="A60" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="B60" s="90"/>
-      <c r="C60" s="91" t="s">
+      <c r="B60" s="97"/>
+      <c r="C60" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="D60" s="91"/>
+      <c r="D60" s="101"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="81">
+      <c r="A61" s="85">
         <v>1002</v>
       </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81" t="str">
+      <c r="B61" s="85"/>
+      <c r="C61" s="85" t="str">
         <f>VLOOKUP($A$61,$A$9:$B$28,2,FALSE)</f>
         <v>Student 2</v>
       </c>
-      <c r="D61" s="81"/>
+      <c r="D61" s="85"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
@@ -2733,46 +2733,46 @@
       <c r="D64" s="22"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="76" t="s">
+      <c r="A65" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="B65" s="77"/>
-      <c r="C65" s="77"/>
-      <c r="D65" s="77"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="78"/>
+      <c r="B65" s="87"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="87"/>
+      <c r="E65" s="87"/>
+      <c r="F65" s="87"/>
+      <c r="G65" s="87"/>
+      <c r="H65" s="88"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="43">
         <v>8</v>
       </c>
-      <c r="B66" s="81" t="s">
+      <c r="B66" s="85" t="s">
         <v>142</v>
       </c>
-      <c r="C66" s="81"/>
-      <c r="D66" s="81"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81"/>
-      <c r="H66" s="81"/>
+      <c r="C66" s="85"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="85"/>
+      <c r="F66" s="85"/>
+      <c r="G66" s="85"/>
+      <c r="H66" s="85"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D67" s="92"/>
-      <c r="E67" s="92"/>
+      <c r="D67" s="98"/>
+      <c r="E67" s="98"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="79" t="s">
+      <c r="A68" s="83" t="s">
         <v>143</v>
       </c>
-      <c r="B68" s="79"/>
+      <c r="B68" s="83"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="80">
+      <c r="A69" s="84">
         <v>80</v>
       </c>
-      <c r="B69" s="80"/>
+      <c r="B69" s="84"/>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
@@ -3007,16 +3007,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="D67:E67"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="A57:H57"/>
     <mergeCell ref="B66:H66"/>
     <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="B2:H2"/>
@@ -3032,6 +3031,7 @@
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A61:B61"/>
+    <mergeCell ref="D67:E67"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A61 B61:B64" xr:uid="{4238A7DD-2C30-417F-B37A-76500483AA09}">
@@ -3068,41 +3068,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="97"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="104"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -3807,15 +3807,15 @@
       <c r="I29" s="25"/>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="95" t="s">
+      <c r="A30" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="97"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="49"/>
       <c r="I30" s="25"/>
     </row>
@@ -3823,14 +3823,14 @@
       <c r="A31" s="18">
         <v>3</v>
       </c>
-      <c r="B31" s="81" t="s">
+      <c r="B31" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85"/>
       <c r="H31" s="49"/>
       <c r="I31" s="25"/>
     </row>
@@ -3852,7 +3852,7 @@
       <c r="B34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="105">
+      <c r="C34" s="77">
         <f>SUMIFS($E$7:$E$25,$C$7:$C$25,$A$34,B$7:B$25,$B$34)</f>
         <v>25010</v>
       </c>
@@ -3878,31 +3878,31 @@
       <c r="C38" s="20"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="95" t="s">
+      <c r="A39" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="96"/>
-      <c r="C39" s="96"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96"/>
-      <c r="F39" s="96"/>
-      <c r="G39" s="97"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="104"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <v>4</v>
       </c>
-      <c r="B40" s="81" t="s">
+      <c r="B40" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="81"/>
-      <c r="G40" s="81"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="85"/>
+      <c r="G40" s="85"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="110" t="s">
+      <c r="A42" s="82" t="s">
         <v>161</v>
       </c>
       <c r="B42" s="44" t="s">
@@ -3973,20 +3973,20 @@
       <c r="C48" s="67"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="101" t="s">
+      <c r="A49" s="105" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="91"/>
+      <c r="B49" s="101"/>
       <c r="C49" s="32" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="89" t="s">
+      <c r="A50" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="109" cm="1">
+      <c r="B50" s="85"/>
+      <c r="C50" s="81" cm="1">
         <f t="array" ref="C50">VLOOKUP(A50,B43:C47,{2},FALSE)</f>
         <v>25000</v>
       </c>
@@ -4007,28 +4007,28 @@
       <c r="C53" s="67"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="95" t="s">
+      <c r="A54" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="96"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="97"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="103"/>
+      <c r="D54" s="103"/>
+      <c r="E54" s="103"/>
+      <c r="F54" s="103"/>
+      <c r="G54" s="104"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
         <v>5</v>
       </c>
-      <c r="B55" s="81" t="s">
+      <c r="B55" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
+      <c r="C55" s="85"/>
+      <c r="D55" s="85"/>
+      <c r="E55" s="85"/>
+      <c r="F55" s="85"/>
+      <c r="G55" s="85"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="71"/>
@@ -4082,34 +4082,34 @@
       <c r="D62" s="33"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="95" t="s">
+      <c r="A63" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B63" s="96"/>
-      <c r="C63" s="96"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="96"/>
-      <c r="F63" s="96"/>
-      <c r="G63" s="97"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="103"/>
+      <c r="D63" s="103"/>
+      <c r="E63" s="103"/>
+      <c r="F63" s="103"/>
+      <c r="G63" s="104"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>6</v>
       </c>
-      <c r="B64" s="81" t="s">
+      <c r="B64" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="C64" s="81"/>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
+      <c r="C64" s="85"/>
+      <c r="D64" s="85"/>
+      <c r="E64" s="85"/>
+      <c r="F64" s="85"/>
+      <c r="G64" s="85"/>
     </row>
     <row r="66" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="100" t="s">
+      <c r="A66" s="108" t="s">
         <v>158</v>
       </c>
-      <c r="B66" s="100"/>
+      <c r="B66" s="108"/>
       <c r="C66" s="40" t="s">
         <v>26</v>
       </c>
@@ -4139,10 +4139,10 @@
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="81" t="s">
+      <c r="A67" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="81"/>
+      <c r="B67" s="85"/>
       <c r="C67" s="17" cm="1">
         <f t="array" ref="C67:K67">_xlfn.XLOOKUP(A67,D7:D26,A7:I26,"-")</f>
         <v>2005</v>
@@ -4165,7 +4165,7 @@
       <c r="I67" s="17" t="str">
         <v>3</v>
       </c>
-      <c r="J67" s="104">
+      <c r="J67" s="76">
         <v>0.4</v>
       </c>
       <c r="K67" s="17" t="str">
@@ -4173,28 +4173,28 @@
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="95" t="s">
+      <c r="A72" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B72" s="96"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="96"/>
-      <c r="E72" s="96"/>
-      <c r="F72" s="96"/>
-      <c r="G72" s="97"/>
+      <c r="B72" s="103"/>
+      <c r="C72" s="103"/>
+      <c r="D72" s="103"/>
+      <c r="E72" s="103"/>
+      <c r="F72" s="103"/>
+      <c r="G72" s="104"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>7</v>
       </c>
-      <c r="B73" s="81" t="s">
+      <c r="B73" s="85" t="s">
         <v>127</v>
       </c>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="81"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
+      <c r="C73" s="85"/>
+      <c r="D73" s="85"/>
+      <c r="E73" s="85"/>
+      <c r="F73" s="85"/>
+      <c r="G73" s="85"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="46" t="s">
@@ -4234,34 +4234,34 @@
       <c r="C80" s="20"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="95" t="s">
+      <c r="A81" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="96"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="96"/>
-      <c r="E81" s="96"/>
-      <c r="F81" s="96"/>
-      <c r="G81" s="97"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="103"/>
+      <c r="D81" s="103"/>
+      <c r="E81" s="103"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="104"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>8</v>
       </c>
-      <c r="B82" s="81" t="s">
+      <c r="B82" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="C82" s="81"/>
-      <c r="D82" s="81"/>
-      <c r="E82" s="81"/>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
+      <c r="C82" s="85"/>
+      <c r="D82" s="85"/>
+      <c r="E82" s="85"/>
+      <c r="F82" s="85"/>
+      <c r="G82" s="85"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="98" t="s">
+      <c r="A84" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="B84" s="99"/>
+      <c r="B84" s="107"/>
       <c r="C84" s="70"/>
       <c r="D84" s="70"/>
     </row>
@@ -4522,28 +4522,28 @@
       <c r="D108" s="68"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="95" t="s">
+      <c r="A109" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="B109" s="96"/>
-      <c r="C109" s="96"/>
-      <c r="D109" s="96"/>
-      <c r="E109" s="96"/>
-      <c r="F109" s="96"/>
-      <c r="G109" s="97"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="103"/>
+      <c r="E109" s="103"/>
+      <c r="F109" s="103"/>
+      <c r="G109" s="104"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="43">
         <v>9</v>
       </c>
-      <c r="B110" s="87" t="s">
+      <c r="B110" s="94" t="s">
         <v>144</v>
       </c>
-      <c r="C110" s="88"/>
-      <c r="D110" s="88"/>
-      <c r="E110" s="88"/>
-      <c r="F110" s="88"/>
-      <c r="G110" s="89"/>
+      <c r="C110" s="95"/>
+      <c r="D110" s="95"/>
+      <c r="E110" s="95"/>
+      <c r="F110" s="95"/>
+      <c r="G110" s="96"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B111" s="22"/>
@@ -4920,6 +4920,9 @@
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A109:G109"/>
     <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="B73:G73"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="A30:G30"/>
@@ -4931,9 +4934,6 @@
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="B73:G73"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="7">
@@ -4981,38 +4981,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="85" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="43">
         <v>2</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="89"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="96"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="H6" s="17">
         <f ca="1">_xlfn.DAYS(TODAY(),E6)</f>
-        <v>4290</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H7" s="17">
         <f t="shared" ref="H7:H25" ca="1" si="2">_xlfn.DAYS(TODAY(),E7)</f>
-        <v>4040</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H8" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>3790</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="H9" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>3540</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="H10" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>3290</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>3040</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>2790</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="H13" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>2540</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="H14" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H16" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H18" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H19" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="H20" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="H21" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="H22" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H23" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="H24" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>-210</v>
+        <v>-209</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="H25" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>-460</v>
+        <v>-459</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5661,14 +5661,14 @@
       <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="103" t="s">
+      <c r="A30" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
     </row>
@@ -5676,13 +5676,13 @@
       <c r="A31" s="11">
         <v>3</v>
       </c>
-      <c r="B31" s="102" t="s">
+      <c r="B31" s="109" t="s">
         <v>118</v>
       </c>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20"/>
@@ -5765,26 +5765,26 @@
       <c r="F39" s="20"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="103" t="s">
+      <c r="A40" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="110"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="110"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="43">
         <v>4</v>
       </c>
-      <c r="B41" s="81" t="s">
+      <c r="B41" s="85" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
@@ -5824,26 +5824,26 @@
       <c r="C48" s="75"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="103" t="s">
+      <c r="A49" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
+      <c r="B49" s="110"/>
+      <c r="C49" s="110"/>
+      <c r="D49" s="110"/>
+      <c r="E49" s="110"/>
+      <c r="F49" s="110"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="43">
         <v>5</v>
       </c>
-      <c r="B50" s="81" t="s">
+      <c r="B50" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="81"/>
-      <c r="F50" s="81"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="85"/>
+      <c r="E50" s="85"/>
+      <c r="F50" s="85"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
